--- a/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
+++ b/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
@@ -9,12 +9,11 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PARTLY BLOCKED" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NOT CHECKED YET" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DEVIATION" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="BLOCKED - DATA MISSING" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DEVIATION" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="NOT OURS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CANNOT BE RUN" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PASS - BUT READ THE NOTE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NOT OURS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CANNOT BE RUN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PASS - BUT READ THE NOTE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -512,14 +511,14 @@
         <v>119</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>PARTLY BLOCKED: 2, NOT CHECKED YET: 2, NOT OURS: 1, BLOCKED - DATA MISSING: 2, DEVIATION: 1</t>
+          <t>PARTLY BLOCKED: 2, DEVIATION: 3, NOT OURS: 1, BLOCKED - DATA MISSING: 1</t>
         </is>
       </c>
     </row>
@@ -533,14 +532,14 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>PARTLY BLOCKED: 1, BLOCKED - DATA MISSING: 5, CANNOT BE RUN: 2</t>
+          <t>PARTLY BLOCKED: 1, CANNOT BE RUN: 5</t>
         </is>
       </c>
     </row>
@@ -590,15 +589,15 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED YET</t>
+          <t>DEVIATION</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>We did not get to it. Leave it Untested unless the row says otherwise.</t>
+          <t>The build genuinely does the wrong thing. Run it, expect it to fail, mark it FAILED.</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -611,7 +610,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -624,7 +623,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>NOT OURS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -632,7 +631,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The build genuinely does the wrong thing. Run it, expect it to fail, mark it FAILED.</t>
+          <t>Somebody else owns this case. Do not run or change it.</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -641,15 +640,15 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NOT OURS</t>
+          <t>CANNOT BE RUN</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Somebody else owns this case. Do not run or change it.</t>
+          <t>The situation the case describes cannot be created at all. Leave it Untested.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -658,36 +657,19 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CANNOT BE RUN</t>
+          <t>PASS - BUT READ THE NOTE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The situation the case describes cannot be created at all. Leave it Untested.</t>
+          <t>It passes, but something on screen differs from the wording in the case.</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>PASS - BUT READ THE NOTE</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>It passes, but something on screen differs from the wording in the case.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -804,7 +786,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RUN THE PART YOU CAN. Open a work order whose status is Paid and check the Add Part button is not there - that part is confirmed working. The other four statuses the case names (Complete, Invoiced, Declined, Imported) do not exist on this test system, so SKIP those and mark the case Blocked with the note "no work order in that status exists here".</t>
+          <t>RUN THE PART YOU CAN. Open a work order whose status is Paid and check the Add Part button is not there - that part is confirmed working. Of the other four the case names, Declined and Imported are not statuses this product has at all (its list is Estimate, Approved, In progress, Review, Complete, Invoiced, Paid), and no work order here is Complete or Invoiced. Mark the case Blocked with the note "only the Paid status could be checked".</t>
         </is>
       </c>
     </row>
@@ -898,7 +880,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>RUN THE THREE YOU CAN. The Print option is confirmed present on Estimate, Approved and Paid work orders. The other seven statuses the case names do not exist on this test system - skip those and mark the case Blocked with the note "only three of the ten statuses exist here".</t>
+          <t>RUN THE THREE YOU CAN. The Print option is confirmed present on Estimate, Approved and Paid work orders. Note that the product itself only has seven work order statuses - Estimate, Approved, In progress, Review, Complete, Invoiced, Paid - and only those three exist in the data here, so mark the case Blocked with the note "only three of the statuses exist here".</t>
         </is>
       </c>
     </row>
@@ -913,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1002,12 +984,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>not exercised by this pass</t>
+          <t>DEVIATION, observed 2026-09-01. S1-N4 requires the "Add Part" button NOT to be displayed when the line is not editable. The line status enum HAS "complete" (GET /api/work-orders/line-statuses), so this was never a data-state gap - nobody had walked it. Walked line 2 of S9315-14846 authorization_required -&gt; authorized -&gt; complete (a direct jump answers 400 naming the allowed transition, and a line with unfulfilled part requests cannot complete at all, so a part-free line is needed). With the badge reading "Complete" the line STILL shows "+ Add Part" in its Parts row - visible in evidence/last3-line-complete.png - and the page-level count of Add Part buttons stays at 3 for 3 lines. Line status restored and the restore verified</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED YET</t>
+          <t>DEVIATION</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1017,19 +999,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>DO NOT RUN IT YET. Nobody knows yet what makes a work order un-editable other than its status, so there is no way to set the situation up. It is waiting on an answer from the product owner. Leave it Untested.</t>
+          <t>RUN IT AND EXPECT IT TO FAIL. Pick a line with NO parts on it, click Approve, then mark it Complete from the same row (going straight to Complete is refused, and a line that has parts cannot be completed at all). With the badge reading "Complete", look at that line's Parts section: the "+ Add Part" button is still there, and it should not be. Mark the case FAILED.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C45034</t>
+          <t>C45060</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45034</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45060</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1039,7 +1021,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Concurrent change by another user fails the edit save with a message</t>
+          <t>Selected part with no cost or sell price opens those fields empty</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1049,12 +1031,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>not exercised by this pass</t>
+          <t>DEVIATION, observed 2026-09-01, and the earlier "the state may not be reachable" was wrong: it was drawn from the INVENTORY list (stocked parts) when the case is about a CATALOGUE part. F40010212 "Slack Adjuster" is a catalogue part whose record carries no cost and no sell-price field at all and which /api/inventory/parts?search= returns nothing for, so it is genuinely priceless. S4-E1 requires those fields to open EMPTY and the user to enter them before saving inline. Selecting it opens cost "0.00" and sell "0.00" - values, not empty - and pressing Save SUCCEEDED: HTTP 201 with the "Part added" confirmation and no "Enter a description, qty, cost and sell price" message. So a part can be added at zero price without the user entering anything, which is what the requirement exists to prevent. The seeded part was removed afterwards</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>NOT CHECKED YET</t>
+          <t>DEVIATION</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1064,7 +1046,54 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>DO NOT RUN IT YET. It needs a second person to change the same part while your edit row is open. If you can get a colleague to do that at the same time, run it; otherwise leave it Untested and tell the QA lead.</t>
+          <t>RUN IT AND EXPECT IT TO FAIL. Click Add Part, type "F40010212" in the Part number box and click the suggestion marked "Catalog" (Slack Adjuster - it is stocked nowhere and has no price on record). The Cost and Sell price boxes should open EMPTY and stop you saving until you fill them; instead they open showing "0.00" and the part saves at 0.00. Mark the case FAILED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C45068</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45068</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Edit while an inline add row is open triggers the guard first</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Edit on a part line while a POPULATED add row is open opens the Edit Part Request modal immediately, with no discard confirmation, and leaves the add row open. Observed twice. S5-E1 requires S6-R5 first.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>RUN IT AND EXPECT IT TO FAIL. Type a part into the inline row without saving, then click the pencil on another part on the same line. The "Discard this part?" question should appear first; it does not - the Edit Part Request window opens straight away and your typed part is left behind it. Mark the case FAILED and add nothing else.</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1143,12 +1172,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C45060</t>
+          <t>C45034</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45060</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45034</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1158,7 +1187,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Selected part with no cost or sell price opens those fields empty</t>
+          <t>Concurrent change by another user fails the edit save with a message</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1168,7 +1197,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>the state may not be reachable either. All 18 zero-price parts on the branch hold 0.00, which is a value rather than an empty field, and the Edit Inventory Part form carries no field with the id the New form uses for cost. Same PO question: does this product ever store a catalog part with NO cost or sell price on record?</t>
+          <t>STILL NOT OBSERVED, and this one is honest rather than unseeded. It needs a genuine second actor changing the same part while the edit row is open. Two attempts: changing the part through the API while the browser row was open, and deleting it outright. Neither produced the documented sentence, but neither run reliably had the edit row open at the moment of the change, so the runs prove nothing either way and are NOT reported as a deviation. A tester with a colleague can settle it in a minute, and the case now says so in its own words</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1183,289 +1212,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>DO NOT RUN IT YET. It needs a part that has no cost and no sell price recorded at all. Every part on this test system has at least 0.00 in those boxes, which is not the same as empty. Waiting on an answer from the product owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>C45239</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45239</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Inline Add and Edit Parts</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>A part with no bins gets no allocation and no chip</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>the state may not be reachable in this product at all. NO inventory part on the branch has zero bins - all 6,879 hold at least one - and the Edit Inventory Part form gives no way to remove the only bin row (the per-row delete appears only once a second row exists). Clearing the bin select and saving left the part byte-identical. Raised as a PO question: if a part can never have zero bins, S7-N1 and the "Not stocked" card may be unreachable by design</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs a part that is not kept in any bin. Every part on this test system is in at least one bin. Waiting on an answer from the product owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>C45090</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45090</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Users without view permission cannot reach the print option</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>needs a user who cannot view the work order at all. The requirement says this is enforced by existing access control rather than by this feature, so proving it means stripping 'Work Orders - View' from a role and confirming the detail page itself is unreachable. Doable the same way the Inline suite proved its permission negative; not run here</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs an account that cannot open work orders at all. Ask the QA lead to set one up, or leave it Untested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>C45097</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45097</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>No customer assigned prints an explicit placeholder</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>needs a work order with no customer assigned. All 100 work orders read carry a customer, so the state does not exist here and was not seeded</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs a work order with no customer on it, and every work order on this test system has one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>C45098</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45098</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>No vehicle assigned prints an explicit placeholder</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>needs a work order with no vehicle assigned. All 100 work orders read carry a vehicle</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs a work order with no vehicle on it, and every work order on this test system has one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>C45104</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45104</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Cancelled lines still print if visible on screen</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>needs a line whose status is Cancelled. No line on the work orders used had that status, and the word "cancel" appears nowhere on the printouts read</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs a line whose status is Cancelled, and none of the work orders checked had one. If you can set a line to Cancelled yourself, do that and then run it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>C45111</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45111</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>A very long tech story wraps and prints in full</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>needs a tech story of 500+ characters. The longest on the work orders used is about 45 characters, so the wrapping behaviour has nothing to demonstrate it</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>BLOCKED - DATA MISSING</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT YET. It needs a tech story at least 500 characters long - roughly a full paragraph. If you can paste that much text into a line's tech story, do that and then run it.</t>
+          <t>THIS ONE REALLY DOES NEED A SECOND PERSON. Ask a colleague to change or delete the same part while your edit row is open, then press Save. If you cannot arrange that, leave it Untested and tell the QA lead - do not guess. We tried it from a second connection rather than a second person and could not get the row open at the right moment, so nothing is known about this behaviour either way.</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1291,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C45068</t>
+          <t>C45220</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45068</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45220</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1559,7 +1306,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Edit while an inline add row is open triggers the guard first</t>
+          <t>Adding a part to a completed line reopens the line</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1569,12 +1316,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Edit on a part line while a POPULATED add row is open opens the Edit Part Request modal immediately, with no discard confirmation, and leaves the add row open. Observed twice. S5-E1 requires S6-R5 first.</t>
+          <t>Vladimir Tomovic's case, flagged Automated — Rules 38 and 71; not touched, not verdicted</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>NOT OURS</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1584,7 +1331,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RUN IT AND EXPECT IT TO FAIL. Type a part into the inline row without saving, then click the pencil on another part on the same line. The "Discard this part?" question should appear first; it does not - the Edit Part Request window opens straight away and your typed part is left behind it. Mark the case FAILED and add nothing else; the ticket for it is already written and waiting on the QA lead.</t>
+          <t>NOT YOURS TO RUN OR CHANGE - this case belongs to Vladimir Tomovic and it has no steps written in it. Leave it alone entirely.</t>
         </is>
       </c>
     </row>
@@ -1594,6 +1341,313 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>C-ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Case title</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>What the document requires</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>What the build actually does (observed)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Freshness</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>What needs to be done</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C45097</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45097</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>No customer assigned prints an explicit placeholder</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>THE STATE CANNOT EXIST ON THIS BUILD, and that is now proved rather than inferred from the 100 work orders that happen to have a customer: pressing Save on the New Work Order dialog with the Customer select empty answers "Customer is a required field" and sends no request at all. So no work order can exist without a customer, and the placeholder this case asks for can never be printed. A product-owner ruling is needed on what the requirement means</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>CANNOT BE RUN</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT RUN IT - it cannot be done. The app will not create a work order without a customer: leaving Customer empty on the New Work Order window answers "Customer is a required field" and nothing is saved. So the printout this case describes can never exist. It is waiting on a product-owner ruling. Leave it Untested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C45098</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45098</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No vehicle assigned prints an explicit placeholder</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>THE STATE CANNOT EXIST ON THIS BUILD. The Asset (vehicle) select shows no required marker, so this was attempted properly: a customer was chosen and Save pressed with the Asset select empty - the dialog answers "Asset is a required field" and sends no request. Nearest real data is S2-6107, whose vehicle carries only a year, and it prints as "Vehicle: 1993", which is a vehicle with sparse data rather than none. A product-owner ruling is needed</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>CANNOT BE RUN</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT RUN IT - it cannot be done, same as the customer one. Choosing a customer and pressing Save with Add Asset empty answers "Asset is a required field". Waiting on a product-owner ruling. Leave it Untested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C45104</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45104</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled lines still print if visible on screen</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>THERE IS NO CANCELLED LINE STATUS IN THE APPLICATION. Asked the build rather than the data: GET /api/work-orders/line-statuses returns exactly authorization_required, authorization_declined, authorized and complete, and posting status "cancelled" against a REAL line id answers 400 with the status field alone rejected as an invalid value. The line's own on-screen action buttons offer only Authorized and Declined. So the case names a status the product does not have - a specification-versus-build question for the PO, not a missing data state</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CANNOT BE RUN</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT RUN IT - there is no "Cancelled" status for a work order line in this product. A line offers only Authorization required, Declined, Authorized and Complete, and those are the only four the system accepts. Waiting on a product-owner ruling. Leave it Untested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C45107</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45107</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No line items prints an explicit placeholder</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>the case cannot be executed as written. On a work order with no lines the Print Work Order item is DISABLED, so the printout - and therefore the "No lines on this work order" placeholder - can never be reached. This is a contradiction inside the specification: the Key Decisions say print is disabled when no line items exist, while this requirement describes what the printout shows in that case. PO question</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>CANNOT BE RUN</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT RUN IT. It cannot be done: on a work order with no lines the Print option is greyed out, so you can never see the printout it describes. The written description contradicts itself here and the product owner has to settle it. Leave it Untested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C45116</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45116</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>With no line items the summary shows zero totals</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>same as C45107 - print is disabled on a work order with no lines, so a zero-totals summary cannot be reached. PO question</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CANNOT BE RUN</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>DO NOT RUN IT - same reason as the case above. You cannot print a work order that has no lines, so there is no summary to look at.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1663,291 +1717,6 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C45220</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45220</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Inline Add and Edit Parts</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Adding a part to a completed line reopens the line</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Vladimir Tomovic's case, flagged Automated — Rules 38 and 71; not touched, not verdicted</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>NOT OURS</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>NOT YOURS TO RUN OR CHANGE - this case belongs to Vladimir Tomovic and it has no steps written in it. Leave it alone entirely.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>C-ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Suite</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Case title</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>What the document requires</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>What the build actually does (observed)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Freshness</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>What needs to be done</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>C45107</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45107</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>No line items prints an explicit placeholder</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>the case cannot be executed as written. On a work order with no lines the Print Work Order item is DISABLED, so the printout - and therefore the "No lines on this work order" placeholder - can never be reached. This is a contradiction inside the specification: the Key Decisions say print is disabled when no line items exist, while this requirement describes what the printout shows in that case. PO question</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>CANNOT BE RUN</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT. It cannot be done: on a work order with no lines the Print option is greyed out, so you can never see the printout it describes. The written description contradicts itself here and the product owner has to settle it. Leave it Untested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>C45116</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45116</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>With no line items the summary shows zero totals</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Printer Friendly Work Orders specification version 8 - see the case's own provenance line for the exact section</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>same as C45107 - print is disabled on a work order with no lines, so a zero-totals summary cannot be reached. PO question</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>CANNOT BE RUN</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>DO NOT RUN IT - same reason as the case above. You cannot print a work order that has no lines, so there is no summary to look at.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="78" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>C-ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Suite</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Case title</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>What the document requires</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>What the build actually does (observed)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Freshness</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>What needs to be done</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
           <t>C45123</t>
         </is>
       </c>

--- a/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
+++ b/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RUN THE PART YOU CAN. Open a work order whose status is Paid and check the Add Part button is not there - that part is confirmed working. Of the other four the case names, Declined and Imported are not statuses this product has at all (its list is Estimate, Approved, In progress, Review, Complete, Invoiced, Paid), and no work order here is Complete or Invoiced. Mark the case Blocked with the note "only the Paid status could be checked".</t>
+          <t>RUN THE PART YOU CAN. The case now names three statuses - Complete, Invoiced, Paid - and only Paid exists in the data here. Open a Paid work order and check the Add Part button is not there; that part is confirmed working. Then mark the case Blocked with the note "only the Paid status could be checked". (Two statuses this case used to name, Declined and Imported, are not statuses this product has at all.)</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Same as the case above, for the pencil (Edit) control instead of the Add Part button.</t>
+          <t>Same as the case above, for the pencil (Edit) control instead of the Add Part button. Note: this case had been narrowed by hand to three statuses and my write pass reverted it; that is repaired, and the case you open now says three.</t>
         </is>
       </c>
     </row>

--- a/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
+++ b/build/handoff-2026-09-01/Inline-Add-and-Edit-Parts_and_Printer-Friendly-Work-Orders_Defects-for-Testers_2026-09-01.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PARTLY BLOCKED" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DEVIATION" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BLOCKED - DATA MISSING" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BLOCKED - DATA MISSING" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DEVIATION" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="NOT OURS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="CANNOT BE RUN" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="PASS - BUT READ THE NOTE" sheetId="7" state="visible" r:id="rId7"/>
@@ -508,17 +508,17 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>112</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>PARTLY BLOCKED: 2, DEVIATION: 3, NOT OURS: 1, BLOCKED - DATA MISSING: 1</t>
+          <t>PARTLY BLOCKED: 2, BLOCKED - DATA MISSING: 3, DEVIATION: 4, NOT OURS: 1</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>BLOCKED - DATA MISSING</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The build genuinely does the wrong thing. Run it, expect it to fail, mark it FAILED.</t>
+          <t>The case is fine but the test system has nothing to run it against yet.</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -606,15 +606,15 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - DATA MISSING</t>
+          <t>DEVIATION</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The case is fine but the test system has nothing to run it against yet.</t>
+          <t>The build genuinely does the wrong thing. Run it, expect it to fail, mark it FAILED.</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Edit control hidden on Complete, Invoiced, Paid, Declined or Imported</t>
+          <t>Edit control hidden on Complete, Invoiced, or Paid</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C44996</t>
+          <t>C45034</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/44996</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45034</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Add Part and Edit hidden when the work order is not editable otherwise</t>
+          <t>Concurrent change by another user fails the edit save with a message</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION, observed 2026-09-01. S1-N4 requires the "Add Part" button NOT to be displayed when the line is not editable. The line status enum HAS "complete" (GET /api/work-orders/line-statuses), so this was never a data-state gap - nobody had walked it. Walked line 2 of S9315-14846 authorization_required -&gt; authorized -&gt; complete (a direct jump answers 400 naming the allowed transition, and a line with unfulfilled part requests cannot complete at all, so a part-free line is needed). With the badge reading "Complete" the line STILL shows "+ Add Part" in its Parts row - visible in evidence/last3-line-complete.png - and the page-level count of Add Part buttons stays at 3 for 3 lines. Line status restored and the restore verified</t>
+          <t>STILL NOT OBSERVED, and this one is honest rather than unseeded. It needs a genuine second actor changing the same part while the edit row is open. Two attempts: changing the part through the API while the browser row was open, and deleting it outright. Neither produced the documented sentence, but neither run reliably had the edit row open at the moment of the change, so the runs prove nothing either way and are NOT reported as a deviation. A tester with a colleague can settle it in a minute, and the case now says so in its own words</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>BLOCKED - DATA MISSING</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RUN IT AND EXPECT IT TO FAIL. Pick a line with NO parts on it, click Approve, then mark it Complete from the same row (going straight to Complete is refused, and a line that has parts cannot be completed at all). With the badge reading "Complete", look at that line's Parts section: the "+ Add Part" button is still there, and it should not be. Mark the case FAILED.</t>
+          <t>THIS ONE REALLY DOES NEED A SECOND PERSON. Ask a colleague to change or delete the same part while your edit row is open, then press Save. If you cannot arrange that, leave it Untested and tell the QA lead - do not guess. We tried it from a second connection rather than a second person and could not get the row open at the right moment, so nothing is known about this behaviour either way.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>C45060</t>
+          <t>C45250</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45060</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45250</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Selected part with no cost or sell price opens those fields empty</t>
+          <t>Completed line does not offer the Add Part option</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION, observed 2026-09-01, and the earlier "the state may not be reachable" was wrong: it was drawn from the INVENTORY list (stocked parts) when the case is about a CATALOGUE part. F40010212 "Slack Adjuster" is a catalogue part whose record carries no cost and no sell-price field at all and which /api/inventory/parts?search= returns nothing for, so it is genuinely priceless. S4-E1 requires those fields to open EMPTY and the user to enter them before saving inline. Selecting it opens cost "0.00" and sell "0.00" - values, not empty - and pressing Save SUCCEEDED: HTTP 201 with the "Part added" confirmation and no "Enter a description, qty, cost and sell price" message. So a part can be added at zero price without the user entering anything, which is what the requirement exists to prevent. The seeded part was removed afterwards</t>
+          <t>NOT OBSERVED, and the blocker is named rather than guessed. His route is the right one - a part must be added AND PICKED before the line can complete - and that is exactly where it stops: a line with an unfulfilled part request answers 400 "Line can`t be completed with unfulfilled part requests." Authorising the line moves the part from "quoted" to "in_stock", which is still not fulfilled, and the part row's own context menu offers only "Move" and "Add Part Fee / Discount" - there is no pick action there, so picking happens elsewhere (the Parts area). What IS known: on a part-FREE line completed on this build the "+ Add Part" button is still shown (evidence/last3-line-complete.png). That is suggestive but it is NOT his state, so no verdict is claimed. Line status restored and verified</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>BLOCKED - DATA MISSING</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1046,19 +1046,19 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>RUN IT AND EXPECT IT TO FAIL. Click Add Part, type "F40010212" in the Part number box and click the suggestion marked "Catalog" (Slack Adjuster - it is stocked nowhere and has no price on record). The Cost and Sell price boxes should open EMPTY and stop you saving until you fill them; instead they open showing "0.00" and the part saves at 0.00. Mark the case FAILED.</t>
+          <t>ONE STEP NEEDS MORE THAN IT SAYS. The line will not go to Complete while a part on it is unfulfilled - the app refuses with "Line can't be completed with unfulfilled part requests." Approving the line moves the part to "In stock", which is still not enough: it has to be PICKED, and the part row's own menu only offers "Move" and "Add Part Fee / Discount", so the pick happens in the Parts area. Pick it, then set the line to Complete, then check the Parts section. If you cannot pick it, mark the case Blocked and say so.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>C45068</t>
+          <t>C45251</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45068</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45251</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Edit while an inline add row is open triggers the guard first</t>
+          <t>Completed line: only the allowed part fields are editable (inventory vs special order)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Edit on a part line while a POPULATED add row is open opens the Edit Part Request modal immediately, with no discard confirmation, and leaves the add row open. Observed twice. S5-E1 requires S6-R5 first.</t>
+          <t>NOT OBSERVED - same blocker as C45250 (the line will not complete until the part is PICKED), and this case additionally needs a special-order part taken through Order → Receive. Neither was reached, so nothing is claimed about which fields stay editable</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>DEVIATION</t>
+          <t>BLOCKED - DATA MISSING</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>RUN IT AND EXPECT IT TO FAIL. Type a part into the inline row without saving, then click the pencil on another part on the same line. The "Discard this part?" question should appear first; it does not - the Edit Part Request window opens straight away and your typed part is left behind it. Mark the case FAILED and add nothing else.</t>
+          <t>SAME BLOCKER as the case above - the part must be PICKED, not just "In stock" - and this one also needs a special-order part taken through Order then Receive. Do both first, then check each field. If you cannot get the line to Complete, mark it Blocked and say which step stopped you.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1172,12 +1172,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C45034</t>
+          <t>C45060</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/45034</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45060</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Concurrent change by another user fails the edit save with a message</t>
+          <t>Selected part with no cost or sell price opens those fields empty</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>STILL NOT OBSERVED, and this one is honest rather than unseeded. It needs a genuine second actor changing the same part while the edit row is open. Two attempts: changing the part through the API while the browser row was open, and deleting it outright. Neither produced the documented sentence, but neither run reliably had the edit row open at the moment of the change, so the runs prove nothing either way and are NOT reported as a deviation. A tester with a colleague can settle it in a minute, and the case now says so in its own words</t>
+          <t>DEVIATION, observed 2026-09-01, and the earlier "the state may not be reachable" was wrong: it was drawn from the INVENTORY list (stocked parts) when the case is about a CATALOGUE part. F40010212 "Slack Adjuster" is a catalogue part whose record carries no cost and no sell-price field at all and which /api/inventory/parts?search= returns nothing for, so it is genuinely priceless. S4-E1 requires those fields to open EMPTY and the user to enter them before saving inline. Selecting it opens cost "0.00" and sell "0.00" - values, not empty - and pressing Save SUCCEEDED: HTTP 201 with the "Part added" confirmation and no "Enter a description, qty, cost and sell price" message. So a part can be added at zero price without the user entering anything, which is what the requirement exists to prevent. The seeded part was removed afterwards</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BLOCKED - DATA MISSING</t>
+          <t>DEVIATION</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1212,7 +1212,148 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>THIS ONE REALLY DOES NEED A SECOND PERSON. Ask a colleague to change or delete the same part while your edit row is open, then press Save. If you cannot arrange that, leave it Untested and tell the QA lead - do not guess. We tried it from a second connection rather than a second person and could not get the row open at the right moment, so nothing is known about this behaviour either way.</t>
+          <t>RUN IT AND EXPECT IT TO FAIL. Click Add Part, type "F40010212" in the Part number box and click the suggestion marked "Catalog" (Slack Adjuster - it is stocked nowhere and has no price on record). The Cost and Sell price boxes should open EMPTY and stop you saving until you fill them; instead they open showing "0.00" and the part saves at 0.00. Mark the case FAILED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C45068</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45068</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Edit while an inline add row is open triggers the guard first</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Edit on a part line while a POPULATED add row is open opens the Edit Part Request modal immediately, with no discard confirmation, and leaves the add row open. Observed twice. S5-E1 requires S6-R5 first.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>RUN IT AND EXPECT IT TO FAIL. Type a part into the inline row without saving, then click the pencil on another part on the same line. The "Discard this part?" question should appear first; it does not - the Edit Part Request window opens straight away and your typed part is left behind it. Mark the case FAILED and add nothing else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C45252</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45252</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Add Part calculates the Sell Price from the cost via the pricing matrix</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION, observed 2026-09-01, and instrumented properly after a first run measured its own instrumentation: assigning .value and dispatching input/change is NOT reliably seen by the component that derives the sell price, so the cost is now TYPED with real key events and Tab. Positive control: picking a stocked part fills cost 53.52 and sell 86.32, so the row does populate prices. Typing the cost to 10.00, 100.00, 200.00 left the sell price at 86.32 every time; on a catalogue part with no price at all it stayed 0.00. Twenty-two pricing matrices are configured (Settings → Pricing), one marked Default, so there is a matrix to apply. Entering the Cost does not fill or recalculate the Sell Price</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>RUN IT AND EXPECT IT TO FAIL. Add a part to a line, enter a Quantity, then enter a Cost. The Sell price should fill in from the pricing matrix; it does not move at all. Checked on a stocked part (cost typed up to 200.00, sell stuck at 86.32) and on a part with no price (stayed 0.00), and 22 pricing matrices are configured, so there is a matrix to apply. Mark the case FAILED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C45253</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/45253</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Changing the part category recalculates the Sell Price via the matrix</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts on Work Order Lines specification version 16 - see the case's own provenance line for the exact section</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION, observed 2026-09-01. The category is an &lt;input&gt;, so its value is read from .value and the change is confirmed from the row label on screen - the first run read innerText, got "" five times and would have called a working control broken. With the label demonstrably moving through Uncategorized → AUTO-Brakes → 70%Override → AUTO-Batteries, the sell price stayed 86.32 throughout. Changing the category does not recalculate the sell price</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>DEVIATION</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>GREEN - checked 1 Sep 2026 on build v26.35.6-598cc8a (0 days old)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>RUN IT AND EXPECT IT TO FAIL. With the add row filled in but not saved, change the Category through a few different ones. The Sell price should change with it; it does not. Tried Uncategorized, AUTO-Brakes, 70%Override and AUTO-Batteries - the category on the row changed every time, the sell price never did. Mark the case FAILED.</t>
         </is>
       </c>
     </row>
